--- a/data/trending_integrated_20260908_09.xlsx
+++ b/data/trending_integrated_20260908_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33050</v>
+        <v>142300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+8.18%</t>
+          <t>+16.35%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>13.33</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>30550</v>
+        <v>122300</v>
       </c>
       <c r="K2" t="n">
-        <v>31650</v>
+        <v>129400</v>
       </c>
       <c r="L2" t="n">
-        <v>33600</v>
+        <v>142300</v>
       </c>
       <c r="M2" t="n">
-        <v>31350</v>
+        <v>128100</v>
       </c>
       <c r="N2" t="n">
-        <v>0.16</v>
+        <v>13.22</v>
       </c>
       <c r="O2" t="n">
-        <v>71111568425</v>
+        <v>52060871700</v>
       </c>
       <c r="P2" t="n">
-        <v>33600</v>
+        <v>198000</v>
       </c>
       <c r="Q2" t="n">
-        <v>8200</v>
+        <v>77100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 세계 최초 반지형 웨어러블 기기 개발 언급. 단기 변동성 및 주의 요구.</t>
+          <t>미국 원전 8기 건설 관련 대형 수주 기대감. 웨스팅하우스 설계 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['웨어러블', '공시', '신규주']</t>
+          <t>['원전', '수주', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90800</v>
+        <v>33000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+3.30%</t>
+          <t>+8.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>1304</v>
+        <v>187</v>
       </c>
       <c r="H3" t="n">
-        <v>23.63</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>87900</v>
+        <v>30550</v>
       </c>
       <c r="K3" t="n">
-        <v>91200</v>
+        <v>31650</v>
       </c>
       <c r="L3" t="n">
-        <v>91700</v>
+        <v>34600</v>
       </c>
       <c r="M3" t="n">
-        <v>90200</v>
+        <v>31350</v>
       </c>
       <c r="N3" t="n">
-        <v>23.53</v>
+        <v>0.16</v>
       </c>
       <c r="O3" t="n">
-        <v>32339180700</v>
+        <v>209947806850</v>
       </c>
       <c r="P3" t="n">
-        <v>139200</v>
+        <v>34600</v>
       </c>
       <c r="Q3" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 관련 원전 8기 수주 기대감 고조. SMR 기술력 부각 및 대규모 투자 유치 가능성.</t>
+          <t>정부 지분 공시 및 신규주로서의 기대감. 주가 조작 의혹 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '투자']</t>
+          <t>['신규주', '지분', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271500</v>
+        <v>93500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+6.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>655</v>
+        <v>198</v>
       </c>
       <c r="F4" t="n">
-        <v>382</v>
+        <v>141</v>
       </c>
       <c r="G4" t="n">
-        <v>3183</v>
+        <v>1401</v>
       </c>
       <c r="H4" t="n">
-        <v>46.79</v>
+        <v>23.63</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>270000</v>
+        <v>87900</v>
       </c>
       <c r="K4" t="n">
-        <v>272000</v>
+        <v>91200</v>
       </c>
       <c r="L4" t="n">
-        <v>272500</v>
+        <v>93500</v>
       </c>
       <c r="M4" t="n">
-        <v>270500</v>
+        <v>90200</v>
       </c>
       <c r="N4" t="n">
-        <v>46.73</v>
+        <v>23.53</v>
       </c>
       <c r="O4" t="n">
-        <v>90199037500</v>
+        <v>118519584400</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q4" t="n">
-        <v>69600</v>
+        <v>57000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+          <t>텍사스 발전 사업 관련 원전 8기 수주 기대감 고조. SMR 기술력 부각 및 대규모 투자 유치 가능성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '자사주']</t>
+          <t>['원전', 'SMR', '투자']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1791000</v>
+        <v>1794000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>755</v>
+        <v>798</v>
       </c>
       <c r="F5" t="n">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="G5" t="n">
-        <v>3368</v>
+        <v>2972</v>
       </c>
       <c r="H5" t="n">
         <v>50.63</v>
@@ -877,16 +877,16 @@
         <v>1799000</v>
       </c>
       <c r="L5" t="n">
-        <v>1799000</v>
+        <v>1800000</v>
       </c>
       <c r="M5" t="n">
-        <v>1784000</v>
+        <v>1777000</v>
       </c>
       <c r="N5" t="n">
         <v>50.5</v>
       </c>
       <c r="O5" t="n">
-        <v>172326340000</v>
+        <v>469178508000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>야간 선물 상승에 따른 주가 상승 기대감 형성. BNK증권 연구원 관련 부정적 언급.</t>
+          <t>야간 선물 상승에 따른 SK하이닉스 주가 상승 기대. 190만원 돌파 및 200만원 터치 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '전망']</t>
+          <t>['야간선물', '전망', '추세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -925,6 +925,98 @@
       <c r="Z5" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>270000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E6" t="n">
+        <v>701</v>
+      </c>
+      <c r="F6" t="n">
+        <v>409</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3253</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>272000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>272500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>269000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>268236231000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['반도체', '선물', '자사주']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260908_09.xlsx
+++ b/data/trending_integrated_20260908_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142300</v>
+        <v>34800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+16.35%</t>
+          <t>+13.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>96</v>
+        <v>236</v>
       </c>
       <c r="H2" t="n">
-        <v>13.33</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>122300</v>
+        <v>30550</v>
       </c>
       <c r="K2" t="n">
-        <v>129400</v>
+        <v>31650</v>
       </c>
       <c r="L2" t="n">
-        <v>142300</v>
+        <v>34800</v>
       </c>
       <c r="M2" t="n">
-        <v>128100</v>
+        <v>31350</v>
       </c>
       <c r="N2" t="n">
-        <v>13.22</v>
+        <v>0.16</v>
       </c>
       <c r="O2" t="n">
-        <v>52060871700</v>
+        <v>287011422325</v>
       </c>
       <c r="P2" t="n">
-        <v>198000</v>
+        <v>34800</v>
       </c>
       <c r="Q2" t="n">
-        <v>77100</v>
+        <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-33000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 원전 8기 건설 관련 대형 수주 기대감. 웨스팅하우스 설계 관련 언급.</t>
+          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 언급. 주가 부양 의지 및 신규주 특성 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['원전', '수주', '웨스팅하우스']</t>
+          <t>['신규주', '정부지분', '기술']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33000</v>
+        <v>136900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+8.02%</t>
+          <t>+11.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>13.33</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30550</v>
+        <v>122300</v>
       </c>
       <c r="K3" t="n">
-        <v>31650</v>
+        <v>129400</v>
       </c>
       <c r="L3" t="n">
-        <v>34600</v>
+        <v>143100</v>
       </c>
       <c r="M3" t="n">
-        <v>31350</v>
+        <v>128100</v>
       </c>
       <c r="N3" t="n">
-        <v>0.16</v>
+        <v>13.22</v>
       </c>
       <c r="O3" t="n">
-        <v>209947806850</v>
+        <v>80610303100</v>
       </c>
       <c r="P3" t="n">
-        <v>34600</v>
+        <v>198000</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>77100</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-62000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 신규주로서의 기대감. 주가 조작 의혹 및 단기 급등 가능성 언급.</t>
+          <t>미국 원전 8기 건설(260조 규모) 수주 기대감. 웨스팅하우스 설계와의 연관성 및 신사업 진출 재료 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규주', '지분', '주포']</t>
+          <t>['원전', '수주', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93500</v>
+        <v>11880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+8.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>198</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>1401</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
-        <v>23.63</v>
+        <v>5.42</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>87900</v>
+        <v>10920</v>
       </c>
       <c r="K4" t="n">
-        <v>91200</v>
+        <v>11300</v>
       </c>
       <c r="L4" t="n">
-        <v>93500</v>
+        <v>12700</v>
       </c>
       <c r="M4" t="n">
-        <v>90200</v>
+        <v>11050</v>
       </c>
       <c r="N4" t="n">
-        <v>23.53</v>
+        <v>5.53</v>
       </c>
       <c r="O4" t="n">
-        <v>118519584400</v>
+        <v>59729969995</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>30200</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 관련 원전 8기 수주 기대감 고조. SMR 기술력 부각 및 대규모 투자 유치 가능성.</t>
+          <t>원전 섹터 전반의 상승세에 따른 기대감. 프랑스와의 원자력 협정 및 공매도 상환 압박 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '투자']</t>
+          <t>['원전', '협정', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1794000</v>
+        <v>19530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+6.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>798</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>426</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>2972</v>
+        <v>155</v>
       </c>
       <c r="H5" t="n">
-        <v>50.63</v>
+        <v>10.47</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1783000</v>
+        <v>18410</v>
       </c>
       <c r="K5" t="n">
-        <v>1799000</v>
+        <v>18800</v>
       </c>
       <c r="L5" t="n">
-        <v>1800000</v>
+        <v>20200</v>
       </c>
       <c r="M5" t="n">
-        <v>1777000</v>
+        <v>18480</v>
       </c>
       <c r="N5" t="n">
-        <v>50.5</v>
+        <v>10.4</v>
       </c>
       <c r="O5" t="n">
-        <v>469178508000</v>
+        <v>116752892720</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>274000</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-133000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>야간 선물 상승에 따른 SK하이닉스 주가 상승 기대. 190만원 돌파 및 200만원 터치 가능성 언급.</t>
+          <t>신사업 재료 발표 기대감 속 원전 관련 긍정적 언급. 하지만 아직 확정된 내용은 없는 상황.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['야간선물', '전망', '추세']</t>
+          <t>['신사업', '원전', '재료']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>270000</v>
+        <v>91900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+4.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>701</v>
+        <v>225</v>
       </c>
       <c r="F6" t="n">
-        <v>409</v>
+        <v>160</v>
       </c>
       <c r="G6" t="n">
-        <v>3253</v>
+        <v>1445</v>
       </c>
       <c r="H6" t="n">
-        <v>46.79</v>
+        <v>23.63</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,58 +963,334 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>270000</v>
+        <v>87900</v>
       </c>
       <c r="K6" t="n">
-        <v>272000</v>
+        <v>91200</v>
       </c>
       <c r="L6" t="n">
-        <v>272500</v>
+        <v>93500</v>
       </c>
       <c r="M6" t="n">
-        <v>269000</v>
+        <v>90200</v>
       </c>
       <c r="N6" t="n">
-        <v>46.73</v>
+        <v>23.53</v>
       </c>
       <c r="O6" t="n">
-        <v>268236231000</v>
+        <v>168885957800</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>69600</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-253000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+          <t>30조 텍사스 발전 사업 포함 원전 8기 건설 등 대규모 수주 기대감. SMR 강자 부각 및 웨스팅하우스 지분 인수 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['원전', 'SMR', '대미투자']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1843000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+3.37%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>797</v>
+      </c>
+      <c r="F7" t="n">
+        <v>446</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1946</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1783000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1799000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1846000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1777000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>986576404000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>274000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>180만원 돌파 및 200만원 터치 가능성 언급. 연말 전고점 돌파 기대감 및 유럽 시장과의 비교 언급.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>0.2</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['180만원', '200만원', '전고점']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>33800</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+3.21%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>42</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>128</v>
+      </c>
+      <c r="H8" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>32750</v>
+      </c>
+      <c r="K8" t="n">
+        <v>33700</v>
+      </c>
+      <c r="L8" t="n">
+        <v>34350</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33600</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26139433400</v>
+      </c>
+      <c r="P8" t="n">
+        <v>69500</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30400</v>
+      </c>
+      <c r="R8" t="n">
+        <v>187000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>웨스팅하우스 지분 인수 및 미국 원전 8기 추진 관련 긍정적 전망. PBR 저평가 해소 기대감 및 공매도 물량 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['원전', '웨스팅하우스', 'PBR']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>273250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+1.20%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>779</v>
+      </c>
+      <c r="F9" t="n">
+        <v>448</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3361</v>
+      </c>
+      <c r="H9" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>272000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>274000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>269000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="O9" t="n">
+        <v>510004004500</v>
+      </c>
+      <c r="P9" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R9" t="n">
+        <v>91000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>['반도체', '선물', '자사주']</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="X9" t="n">
         <v>101</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>005930</t>
         </is>

--- a/data/trending_integrated_20260908_09.xlsx
+++ b/data/trending_integrated_20260908_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34800</v>
+        <v>3640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+13.91%</t>
+          <t>+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>175</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>236</v>
+        <v>59</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>30550</v>
+        <v>2800</v>
       </c>
       <c r="K2" t="n">
-        <v>31650</v>
+        <v>2900</v>
       </c>
       <c r="L2" t="n">
-        <v>34800</v>
+        <v>3640</v>
       </c>
       <c r="M2" t="n">
-        <v>31350</v>
+        <v>2900</v>
       </c>
       <c r="N2" t="n">
-        <v>0.16</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>287011422325</v>
+        <v>115796227613</v>
       </c>
       <c r="P2" t="n">
-        <v>34800</v>
+        <v>8100</v>
       </c>
       <c r="Q2" t="n">
-        <v>8200</v>
+        <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>-33000</v>
+        <v>662000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 언급. 주가 부양 의지 및 신규주 특성 관련 언급.</t>
+          <t>AI 및 6G 광통신 부품 국책 사업 선정 기반 주가 상승 기대. 외국인 매수세 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규주', '정부지분', '기술']</t>
+          <t>['AI', '광통신', '국책사업']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136900</v>
+        <v>36250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+11.94%</t>
+          <t>+18.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>367</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>423</v>
       </c>
       <c r="H3" t="n">
-        <v>13.33</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>122300</v>
+        <v>30550</v>
       </c>
       <c r="K3" t="n">
-        <v>129400</v>
+        <v>31650</v>
       </c>
       <c r="L3" t="n">
-        <v>143100</v>
+        <v>39350</v>
       </c>
       <c r="M3" t="n">
-        <v>128100</v>
+        <v>31350</v>
       </c>
       <c r="N3" t="n">
-        <v>13.22</v>
+        <v>0.16</v>
       </c>
       <c r="O3" t="n">
-        <v>80610303100</v>
+        <v>564837237975</v>
       </c>
       <c r="P3" t="n">
-        <v>198000</v>
+        <v>39350</v>
       </c>
       <c r="Q3" t="n">
-        <v>77100</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
-        <v>-62000</v>
+        <v>-33000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 원전 8기 건설(260조 규모) 수주 기대감. 웨스팅하우스 설계와의 연관성 및 신사업 진출 재료 언급.</t>
+          <t>신규 상장주로서 주포 활동 및 5만원, 7~8만원 목표 제시. 매출 대비 큰 손실 구조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['원전', '수주', '웨스팅하우스']</t>
+          <t>['신규주', '주포', '시총']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11880</v>
+        <v>138300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>+13.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="H4" t="n">
-        <v>5.42</v>
+        <v>13.33</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10920</v>
+        <v>122300</v>
       </c>
       <c r="K4" t="n">
-        <v>11300</v>
+        <v>129400</v>
       </c>
       <c r="L4" t="n">
-        <v>12700</v>
+        <v>143100</v>
       </c>
       <c r="M4" t="n">
-        <v>11050</v>
+        <v>128100</v>
       </c>
       <c r="N4" t="n">
-        <v>5.53</v>
+        <v>13.22</v>
       </c>
       <c r="O4" t="n">
-        <v>59729969995</v>
+        <v>119964268000</v>
       </c>
       <c r="P4" t="n">
-        <v>30200</v>
+        <v>198000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3540</v>
+        <v>77100</v>
       </c>
       <c r="R4" t="n">
-        <v>-249000</v>
+        <v>-62000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승세에 따른 기대감. 프랑스와의 원자력 협정 및 공매도 상환 압박 언급.</t>
+          <t>미국 원전 8기 수주 가능성 및 AP1000 관련 사업 내용 언급, 단기 고점 및 시세 끝 가능성도 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', '협정', '공매도']</t>
+          <t>['원전', 'AP1000', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19530</v>
+        <v>19730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+6.08%</t>
+          <t>+7.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="H5" t="n">
         <v>10.47</v>
@@ -886,7 +886,7 @@
         <v>10.4</v>
       </c>
       <c r="O5" t="n">
-        <v>116752892720</v>
+        <v>179220947935</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신사업 재료 발표 기대감 속 원전 관련 긍정적 언급. 하지만 아직 확정된 내용은 없는 상황.</t>
+          <t>원전 사업 확대 및 상반기 순이익 2745% 성장 기반 3만원 목표 전망. 신규 사업 재료 발표 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신사업', '원전', '재료']</t>
+          <t>['원전', '신사업', '순이익']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91900</v>
+        <v>319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+4.55%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>1445</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>23.63</v>
+        <v>5.34</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>87900</v>
+        <v>299</v>
       </c>
       <c r="K6" t="n">
-        <v>91200</v>
+        <v>220</v>
       </c>
       <c r="L6" t="n">
-        <v>93500</v>
+        <v>344</v>
       </c>
       <c r="M6" t="n">
-        <v>90200</v>
+        <v>220</v>
       </c>
       <c r="N6" t="n">
-        <v>23.53</v>
+        <v>5.29</v>
       </c>
       <c r="O6" t="n">
-        <v>168885957800</v>
+        <v>4393579975</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>901</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>217</v>
       </c>
       <c r="R6" t="n">
-        <v>-253000</v>
+        <v>687000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>30조 텍사스 발전 사업 포함 원전 8기 건설 등 대규모 수주 기대감. SMR 강자 부각 및 웨스팅하우스 지분 인수 관련 뉴스 언급.</t>
+          <t>상장 폐지 우려 속 정매 마지막 불꽃 및 1500원 이상 가치 주장. 회사 자산 대비 시총 괴리 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '대미투자']</t>
+          <t>['상폐', '정매', '자산']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1843000</v>
+        <v>14370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>797</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>446</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>1946</v>
+        <v>238</v>
       </c>
       <c r="H7" t="n">
-        <v>50.63</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1783000</v>
+        <v>13470</v>
       </c>
       <c r="K7" t="n">
-        <v>1799000</v>
+        <v>13580</v>
       </c>
       <c r="L7" t="n">
-        <v>1846000</v>
+        <v>14380</v>
       </c>
       <c r="M7" t="n">
-        <v>1777000</v>
+        <v>13420</v>
       </c>
       <c r="N7" t="n">
-        <v>50.5</v>
+        <v>1.82</v>
       </c>
       <c r="O7" t="n">
-        <v>986576404000</v>
+        <v>104501558690</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>274000</v>
+        <v>1252</v>
       </c>
       <c r="R7" t="n">
-        <v>25000</v>
+        <v>267000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>180만원 돌파 및 200만원 터치 가능성 언급. 연말 전고점 돌파 기대감 및 유럽 시장과의 비교 언급.</t>
+          <t>Texas 소식 기반 상승 기대감, 빛과전자와의 비교 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['180만원', '200만원', '전고점']</t>
+          <t>['Texas', '광통신주', '품절주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33800</v>
+        <v>11570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>+5.95%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H8" t="n">
-        <v>52.7</v>
+        <v>5.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>32750</v>
+        <v>10920</v>
       </c>
       <c r="K8" t="n">
-        <v>33700</v>
+        <v>11300</v>
       </c>
       <c r="L8" t="n">
-        <v>34350</v>
+        <v>12700</v>
       </c>
       <c r="M8" t="n">
-        <v>33600</v>
+        <v>11050</v>
       </c>
       <c r="N8" t="n">
-        <v>21.02</v>
+        <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>26139433400</v>
+        <v>81237175970</v>
       </c>
       <c r="P8" t="n">
-        <v>69500</v>
+        <v>30200</v>
       </c>
       <c r="Q8" t="n">
-        <v>30400</v>
+        <v>3540</v>
       </c>
       <c r="R8" t="n">
-        <v>187000</v>
+        <v>-249000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 미국 원전 8기 추진 관련 긍정적 전망. PBR 저평가 해소 기대감 및 공매도 물량 언급.</t>
+          <t>프랑스와의 원자력 협정 및 공매도 상환 기대, 원전 섹터 전반의 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', 'PBR']</t>
+          <t>['원전', '프랑스', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273250</v>
+        <v>50200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>779</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>448</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>3361</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
-        <v>46.79</v>
+        <v>38.34</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,704 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>270000</v>
+        <v>48000</v>
       </c>
       <c r="K9" t="n">
-        <v>272000</v>
+        <v>48550</v>
       </c>
       <c r="L9" t="n">
-        <v>274000</v>
+        <v>51600</v>
       </c>
       <c r="M9" t="n">
-        <v>269000</v>
+        <v>48350</v>
       </c>
       <c r="N9" t="n">
-        <v>46.73</v>
+        <v>38.24</v>
       </c>
       <c r="O9" t="n">
-        <v>510004004500</v>
+        <v>75138864650</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>69600</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>91000</v>
+        <v>286000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+          <t>5만원 돌파 및 캡상승 기대감 존재. 조만간 공시 예정 및 공매도 관련 언급. 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['공시', '공매도', '개인매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>91600</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+4.21%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>274</v>
+      </c>
+      <c r="F10" t="n">
+        <v>190</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1523</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>87900</v>
+      </c>
+      <c r="K10" t="n">
+        <v>91200</v>
+      </c>
+      <c r="L10" t="n">
+        <v>93500</v>
+      </c>
+      <c r="M10" t="n">
+        <v>90200</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="O10" t="n">
+        <v>222076519650</v>
+      </c>
+      <c r="P10" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-253000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['원전', 'SMR', '텍사스']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1842000</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+3.31%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>795</v>
+      </c>
+      <c r="F11" t="n">
+        <v>466</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1817</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1783000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1799000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1848000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1777000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1672870603500</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>274000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>180 돌파 및 박스권 돌파에 대한 기대감, 외인 매수세 유입 관찰 및 전고점 돌파 전망.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['박스권 돌파', '외인 매수', '전고점']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>33800</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+3.21%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" t="n">
+        <v>164</v>
+      </c>
+      <c r="H12" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>32750</v>
+      </c>
+      <c r="K12" t="n">
+        <v>33700</v>
+      </c>
+      <c r="L12" t="n">
+        <v>34350</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33600</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="O12" t="n">
+        <v>35535850625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>69500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>30400</v>
+      </c>
+      <c r="R12" t="n">
+        <v>199000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 원전 8기 추진 및 웨스팅하우스 지분 인수 관련 기대감. PBR 0.48 대비 상승 여력 존재.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['원전', '웨스팅하우스', 'PBR']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>274000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+1.48%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E13" t="n">
+        <v>797</v>
+      </c>
+      <c r="F13" t="n">
+        <v>460</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2324</v>
+      </c>
+      <c r="H13" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>272000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>275000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>269000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1053166192000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R13" t="n">
+        <v>122000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>자사주 매수 200만주 신청 및 15조 규모 자사주 매입 계획에 따른 주가 상승 기대. 휴머노이드 기대감 존재.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['자사주매입', '휴머노이드', '주주환원']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3605</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3580</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3600</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3820</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3450</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>48935572352</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3900</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1246</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-123000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>탈모 치료제 건보 적용 시 급등 기대감. 월가 탈모주 금광 언급 및 바이오니아 상승세 주목.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>0.2</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['반도체', '선물', '자사주']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
-        <v>101</v>
-      </c>
-      <c r="Y9" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['탈모', '건보', '바이오니아']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>005930</t>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>067290</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10060</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43</v>
+      </c>
+      <c r="G15" t="n">
+        <v>41</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>10200</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10600</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10970</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10010</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>47629326690</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R15" t="n">
+        <v>24000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>가스터빈 수주 기대와 미국 독점 공급 가능성 언급, 매수세 관찰 및 보수적 전망.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['가스터빈', '수주', '미국']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15480</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-3.91%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>57</v>
+      </c>
+      <c r="F16" t="n">
+        <v>39</v>
+      </c>
+      <c r="G16" t="n">
+        <v>198</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>16110</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16130</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16140</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15310</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>21697855700</v>
+      </c>
+      <c r="P16" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-41000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>대미 투자 1호 가스 복합 발전소 수주 기대감 있으나, 주가 하락 및 15천원 이탈 우려. 광주 공항 재개장 언급.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['대미투자', '가스발전', '광주공항']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>002990</t>
         </is>
       </c>
     </row>
